--- a/Data/Padron_y_Maestro_Jugadores_CLC_v2.xlsx
+++ b/Data/Padron_y_Maestro_Jugadores_CLC_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jsaravid\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://everisgroup-my.sharepoint.com/personal/jsaravid_emeal_nttdata_com/Documents/Desktop/verbose-system/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D539B75-5E05-4C58-9C60-F96521AA5803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{2D539B75-5E05-4C58-9C60-F96521AA5803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D959644C-A4CE-4E5C-8361-F0A77D40A04A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12300,4 +12300,10 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{3048dc87-43f0-4100-9acb-ae1971c79395}" enabled="0" method="" siteId="{3048dc87-43f0-4100-9acb-ae1971c79395}" removed="1"/>
+</clbl:labelList>
 </file>